--- a/Employee_Reports_wi52/Mark Roentgen Macatangay Delen Q0619.xlsx
+++ b/Employee_Reports_wi52/Mark Roentgen Macatangay Delen Q0619.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1145,11 +1145,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1194,11 +1194,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1244,11 +1244,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1428,11 +1428,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1514,11 +1514,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1563,11 +1563,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1612,11 +1612,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1661,11 +1661,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1698,11 +1698,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1747,11 +1747,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1796,11 +1796,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1833,11 +1833,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Docking Station (QNL Trainings)</t>
+          <t>Reshelving Cart (QNL Trainings)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
@@ -1861,20 +1861,20 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>04-Aug-2026</t>
+          <t>22-Jul-2026</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>03-Aug-2028</t>
+          <t>21-Jul-2028</t>
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>RFID  Security  Gates.1 (QNL Trainings)</t>
+          <t>Library Bin (QNL Trainings)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
@@ -1898,28 +1898,102 @@
       <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
+          <t>22-Jul-2026</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>21-Jul-2028</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>693</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Checkout Station (QNL Trainings)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>22-Jul-2026</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>21-Jul-2028</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>693</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Docking Station (QNL Trainings)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
           <t>04-Aug-2026</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>03-Aug-2028</t>
         </is>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>714</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="n">
+        <v>706</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2338,7 +2412,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2433,7 +2507,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2462,7 +2536,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2565,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2520,7 +2594,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2623,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2578,7 +2652,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2607,7 +2681,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2636,7 +2710,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
